--- a/RTP Resources/RTP_Delivery_Planning.xlsx
+++ b/RTP Resources/RTP_Delivery_Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/RTP Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{0B4D481B-A51D-3A41-AB23-50326DC0D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7654B52D-2593-C54F-B8F0-1066AD538CF4}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="8_{0B4D481B-A51D-3A41-AB23-50326DC0D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E384B46-AA39-5B4D-BE0D-A0DC6259E792}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FFEF5CE7-C993-9145-B48B-4798C2B47F70}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="day_rates">DayRates!$A$1:$B$5</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>PS1</t>
   </si>
@@ -108,7 +108,37 @@
     <t>Est. Monthly Cost</t>
   </si>
   <si>
-    <t>Est. 24 week commit</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>-15 hours per week of S&amp;C service delivery is an estimated average with high variance</t>
+  </si>
+  <si>
+    <t>-This is the estimated time allocation above and beyond normal service delivery</t>
+  </si>
+  <si>
+    <t>-Estimated hours reflect a middle ground between a high-maintenance and low-maintenance rehab</t>
+  </si>
+  <si>
+    <t>-Majority of workload could occur between weeks 4-32, hence the 28 week cost estimate</t>
+  </si>
+  <si>
+    <t>-Hours spent on "planning" may be made more efficient by implementation of the CSIP RTP Protocol</t>
+  </si>
+  <si>
+    <t>-Hours of "In Person Delivery" should not decrease with implementation of the protocol</t>
+  </si>
+  <si>
+    <t>-Contributions from Physiology, Nutrition and Mental Perf are crucial but, time commitment may be considered negligible</t>
+  </si>
+  <si>
+    <t>-Service delivery will almost always be provided by PS2 or PS3 practitioner</t>
+  </si>
+  <si>
+    <t>Est. 28 week commit</t>
+  </si>
+  <si>
+    <t>-Actual RTP service may last 36-52 weeks</t>
   </si>
 </sst>
 </file>
@@ -117,9 +147,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -154,6 +184,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -170,13 +207,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -194,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -203,20 +240,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -552,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E87CDA2-9427-7449-B447-D1E340E46B48}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="18.33203125" customWidth="1"/>
@@ -562,10 +601,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="5"/>
       <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
@@ -580,22 +619,22 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -649,7 +688,10 @@
       </c>
       <c r="B5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <f t="shared" ref="E5:E7" si="0">D5/8</f>
+        <v>0</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -661,7 +703,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -673,7 +718,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -698,94 +746,138 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9">
         <f>SUM(D3:D9)</f>
         <v>15</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="9">
         <f>D10/8</f>
         <v>1.875</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="10">
         <f>INDEX(DayRates!$B:$B,MATCH(F$2,DayRates!$A:$A,0))*$E$10</f>
         <v>468.75</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="10">
         <f>INDEX(DayRates!$B:$B,MATCH(G$2,DayRates!$A:$A,0))*$E$10</f>
         <v>656.25</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="10">
         <f>INDEX(DayRates!$B:$B,MATCH(H$2,DayRates!$A:$A,0))*$E$10</f>
         <v>843.75</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="10">
         <f>INDEX(DayRates!$B:$B,MATCH(I$2,DayRates!$A:$A,0))*$E$10</f>
         <v>1031.25</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="11">
         <f>F10*4</f>
         <v>1875</v>
       </c>
-      <c r="G13" s="9">
-        <f t="shared" ref="G13:I13" si="0">G10*4</f>
+      <c r="G13" s="11">
+        <f t="shared" ref="G13:I13" si="1">G10*4</f>
         <v>2625</v>
       </c>
-      <c r="H13" s="9">
-        <f t="shared" si="0"/>
+      <c r="H13" s="11">
+        <f t="shared" si="1"/>
         <v>3375</v>
       </c>
-      <c r="I13" s="9">
-        <f t="shared" si="0"/>
+      <c r="I13" s="11">
+        <f t="shared" si="1"/>
         <v>4125</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="11">
+        <f>F10*28</f>
+        <v>13125</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" ref="G14:I14" si="2">G10*28</f>
+        <v>18375</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" si="2"/>
+        <v>23625</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="2"/>
+        <v>28875</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="9">
-        <f>F10*24</f>
-        <v>11250</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" ref="G14:I14" si="1">G10*24</f>
-        <v>15750</v>
-      </c>
-      <c r="H14" s="9">
-        <f t="shared" si="1"/>
-        <v>20250</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="1"/>
-        <v>24750</v>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C20">
-        <f>450/8</f>
-        <v>56.25</v>
+      <c r="C20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C22" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C24" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C25" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C26" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
